--- a/histograms/histogram_Oxygen_concentration_avg.xlsx
+++ b/histograms/histogram_Oxygen_concentration_avg.xlsx
@@ -442,15 +442,15 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.01240231838325672</v>
+        <v>0.01229523466060881</v>
       </c>
       <c r="B2" t="n">
-        <v>160</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.01507109923724079</v>
+        <v>0.01474984806929706</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
@@ -458,146 +458,146 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.01773988009122486</v>
+        <v>0.01720446147798531</v>
       </c>
       <c r="B4" t="n">
-        <v>370</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.02040866094520892</v>
+        <v>0.01965907488667355</v>
       </c>
       <c r="B5" t="n">
-        <v>510</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.02307744179919299</v>
+        <v>0.0221136882953618</v>
       </c>
       <c r="B6" t="n">
-        <v>1475</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.02574622265317706</v>
+        <v>0.02456830170405005</v>
       </c>
       <c r="B7" t="n">
-        <v>291</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.02841500350716113</v>
+        <v>0.02702291511273829</v>
       </c>
       <c r="B8" t="n">
-        <v>2768</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.03108378436114519</v>
+        <v>0.02947752852142654</v>
       </c>
       <c r="B9" t="n">
-        <v>1177</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.03375256521512926</v>
+        <v>0.03193214193011479</v>
       </c>
       <c r="B10" t="n">
-        <v>1861</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.03642134606911333</v>
+        <v>0.03438675533880303</v>
       </c>
       <c r="B11" t="n">
-        <v>1771</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.03909012692309739</v>
+        <v>0.03684136874749128</v>
       </c>
       <c r="B12" t="n">
-        <v>4427</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.04175890777708146</v>
+        <v>0.03929598215617953</v>
       </c>
       <c r="B13" t="n">
-        <v>3686</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.04442768863106553</v>
+        <v>0.04175059556486778</v>
       </c>
       <c r="B14" t="n">
-        <v>2382</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.0470964694850496</v>
+        <v>0.04420520897355602</v>
       </c>
       <c r="B15" t="n">
-        <v>1594</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.04976525033903366</v>
+        <v>0.04665982238224427</v>
       </c>
       <c r="B16" t="n">
-        <v>1532</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.05243403119301773</v>
+        <v>0.04911443579093252</v>
       </c>
       <c r="B17" t="n">
-        <v>276</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.05510281204700179</v>
+        <v>0.05156904919962076</v>
       </c>
       <c r="B18" t="n">
-        <v>1756</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.05777159290098587</v>
+        <v>0.05402366260830901</v>
       </c>
       <c r="B19" t="n">
-        <v>128</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.06044037375496993</v>
+        <v>0.05647827601699726</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.063109154608954</v>
+        <v>0.0589328894256855</v>
       </c>
       <c r="B21" t="n">
-        <v>235</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
